--- a/90313_REPORT_BOTTEGA_09-01-2026.xlsx
+++ b/90313_REPORT_BOTTEGA_09-01-2026.xlsx
@@ -9,13 +9,12 @@
     <sheet name="VENDUTO FASCIA ORARIA" r:id="rId3" sheetId="1"/>
     <sheet name="ANALISI ARTICOLI" r:id="rId4" sheetId="2"/>
     <sheet name="PDT VENUTI FS GIORNALIERO" r:id="rId5" sheetId="3"/>
-    <sheet name="INGRESSI" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="53">
   <si>
     <t>FASCIA ORARIA</t>
   </si>
@@ -50,39 +49,6 @@
     <t>15:00 - 15:59</t>
   </si>
   <si>
-    <t>16:00 - 16:59</t>
-  </si>
-  <si>
-    <t>17:00 - 17:59</t>
-  </si>
-  <si>
-    <t>18:00 - 18:59</t>
-  </si>
-  <si>
-    <t>19:00 - 19:59</t>
-  </si>
-  <si>
-    <t>20:00 - 20:59</t>
-  </si>
-  <si>
-    <t>21:00 - 21:59</t>
-  </si>
-  <si>
-    <t>22:00 - 22:59</t>
-  </si>
-  <si>
-    <t>23:00 - 23:59</t>
-  </si>
-  <si>
-    <t>0:00 - 0:59</t>
-  </si>
-  <si>
-    <t>1:00 - 1:59</t>
-  </si>
-  <si>
-    <t>2:00 - 2:59</t>
-  </si>
-  <si>
     <t>TOTALE INCASSI 09/01/2026</t>
   </si>
   <si>
@@ -125,16 +91,22 @@
     <t>Tagliata Pollo</t>
   </si>
   <si>
+    <t>50-004-011-001480</t>
+  </si>
+  <si>
+    <t>Grigliata bovino</t>
+  </si>
+  <si>
     <t>50-004-011-000610</t>
   </si>
   <si>
     <t>Grigliata Mista Xxl</t>
   </si>
   <si>
-    <t>50-004-011-000590</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filetto B.A. </t>
+    <t>50-004-011-000660</t>
+  </si>
+  <si>
+    <t>Salsiccia Toscana (2 Pz.)</t>
   </si>
   <si>
     <t>50-004-011-000860</t>
@@ -143,66 +115,48 @@
     <t>Patate Al Forno</t>
   </si>
   <si>
+    <t>50-004-011-000710</t>
+  </si>
+  <si>
+    <t>Etrusca Marinata Birra (Con Patate)</t>
+  </si>
+  <si>
+    <t>50-004-011-000600</t>
+  </si>
+  <si>
+    <t>Grigliata Mista</t>
+  </si>
+  <si>
+    <t>50-004-011-001370</t>
+  </si>
+  <si>
+    <t>Verdure Grigliate</t>
+  </si>
+  <si>
+    <t>50-004-011-000850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insalata Mista </t>
+  </si>
+  <si>
+    <t>50-004-011-002030</t>
+  </si>
+  <si>
+    <t>Insalata di pollo</t>
+  </si>
+  <si>
+    <t>50-004-011-002020</t>
+  </si>
+  <si>
+    <t>Pane</t>
+  </si>
+  <si>
     <t>50-004-011-000560</t>
   </si>
   <si>
     <t>Arrosticini Di Pecora</t>
   </si>
   <si>
-    <t>50-004-011-000710</t>
-  </si>
-  <si>
-    <t>Etrusca Marinata Birra (Con Patate)</t>
-  </si>
-  <si>
-    <t>50-004-011-000660</t>
-  </si>
-  <si>
-    <t>Salsiccia Toscana (2 Pz.)</t>
-  </si>
-  <si>
-    <t>50-004-011-000600</t>
-  </si>
-  <si>
-    <t>Grigliata Mista</t>
-  </si>
-  <si>
-    <t>50-004-011-001480</t>
-  </si>
-  <si>
-    <t>Grigliata bovino</t>
-  </si>
-  <si>
-    <t>50-004-011-002030</t>
-  </si>
-  <si>
-    <t>Insalata di pollo</t>
-  </si>
-  <si>
-    <t>50-004-011-000740</t>
-  </si>
-  <si>
-    <t>Pulled Pork (Con Patate)</t>
-  </si>
-  <si>
-    <t>50-004-011-001370</t>
-  </si>
-  <si>
-    <t>Verdure Grigliate</t>
-  </si>
-  <si>
-    <t>50-004-011-002020</t>
-  </si>
-  <si>
-    <t>Pane</t>
-  </si>
-  <si>
-    <t>50-004-011-000850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insalata Mista </t>
-  </si>
-  <si>
     <t>TOTALE GRUPPO</t>
   </si>
   <si>
@@ -219,21 +173,6 @@
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>16:00-18:59</t>
-  </si>
-  <si>
-    <t>19:00-02:59</t>
-  </si>
-  <si>
-    <t>09/01/2026</t>
-  </si>
-  <si>
-    <t>VAR %</t>
-  </si>
-  <si>
-    <t>10/01/2025</t>
   </si>
 </sst>
 </file>
@@ -371,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true"/>
@@ -384,27 +323,13 @@
     <xf numFmtId="4" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.59375" customWidth="true" bestFit="true"/>
@@ -492,115 +417,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="2">
+      <c r="A11" t="s" s="1">
         <v>11</v>
       </c>
-      <c r="B11" t="n" s="5">
-        <v>0.0</v>
+      <c r="B11" t="n" s="1">
+        <v>334.27</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="4">
+      <c r="A12" t="s" s="1">
         <v>12</v>
       </c>
-      <c r="B12" t="n" s="7">
-        <v>0.0</v>
+      <c r="B12" t="n" s="1">
+        <v>558.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="2">
+      <c r="A13" t="s" s="1">
         <v>13</v>
       </c>
-      <c r="B13" t="n" s="5">
-        <v>13.6364</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="4">
-        <v>14</v>
-      </c>
-      <c r="B14" t="n" s="7">
-        <v>62.5455</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="B15" t="n" s="5">
-        <v>175.2729</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="4">
-        <v>16</v>
-      </c>
-      <c r="B16" t="n" s="7">
-        <v>89.7273</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="B17" t="n" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="4">
-        <v>18</v>
-      </c>
-      <c r="B18" t="n" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B19" t="n" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="4">
-        <v>20</v>
-      </c>
-      <c r="B20" t="n" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B21" t="n" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="1">
-        <v>22</v>
-      </c>
-      <c r="B22" t="n" s="1">
-        <v>675.45</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="1">
-        <v>23</v>
-      </c>
-      <c r="B23" t="n" s="1">
-        <v>1104.73</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B24" t="n" s="1">
-        <v>-38.86</v>
+      <c r="B13" t="n" s="1">
+        <v>-40.09</v>
       </c>
     </row>
   </sheetData>
@@ -610,7 +447,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -622,305 +459,271 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s" s="4">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n" s="7">
-        <v>151.6365</v>
+        <v>88.4546</v>
       </c>
       <c r="D2" t="n" s="7">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="E2" t="n" s="7">
-        <v>22.45</v>
+        <v>26.46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n" s="5">
-        <v>127.2727</v>
+        <v>63.6363</v>
       </c>
       <c r="D3" t="n" s="5">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="E3" t="n" s="5">
-        <v>18.84</v>
+        <v>19.04</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n" s="7">
-        <v>56.2818</v>
+        <v>35.1818</v>
       </c>
       <c r="D4" t="n" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="E4" t="n" s="7">
-        <v>8.33</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n" s="5">
-        <v>47.091</v>
+        <v>27.2727</v>
       </c>
       <c r="D5" t="n" s="5">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E5" t="n" s="5">
-        <v>6.97</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n" s="7">
-        <v>38.1818</v>
+        <v>23.5455</v>
       </c>
       <c r="D6" t="n" s="7">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E6" t="n" s="7">
-        <v>5.65</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C7" t="n" s="5">
-        <v>36.3637</v>
+        <v>19.8182</v>
       </c>
       <c r="D7" t="n" s="5">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="E7" t="n" s="5">
-        <v>5.38</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n" s="7">
-        <v>33.8182</v>
+        <v>18.1818</v>
       </c>
       <c r="D8" t="n" s="7">
-        <v>31.0</v>
+        <v>5.0</v>
       </c>
       <c r="E8" t="n" s="7">
-        <v>5.01</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n" s="5">
-        <v>30.7272</v>
+        <v>15.3636</v>
       </c>
       <c r="D9" t="n" s="5">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E9" t="n" s="5">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n" s="7">
-        <v>29.7273</v>
+        <v>14.4545</v>
       </c>
       <c r="D10" t="n" s="7">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="E10" t="n" s="7">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n" s="5">
-        <v>28.909</v>
+        <v>7.2728</v>
       </c>
       <c r="D11" t="n" s="5">
         <v>2.0</v>
       </c>
       <c r="E11" t="n" s="5">
-        <v>4.28</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C12" t="n" s="7">
-        <v>27.2727</v>
+        <v>7.2727</v>
       </c>
       <c r="D12" t="n" s="7">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E12" t="n" s="7">
-        <v>4.04</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n" s="5">
-        <v>21.8181</v>
+        <v>7.2727</v>
       </c>
       <c r="D13" t="n" s="5">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="E13" t="n" s="5">
-        <v>3.23</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="4">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C14" t="n" s="7">
-        <v>14.5455</v>
+        <v>5.4546</v>
       </c>
       <c r="D14" t="n" s="7">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="E14" t="n" s="7">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C15" t="n" s="5">
-        <v>13.8092</v>
+        <v>1.0909</v>
       </c>
       <c r="D15" t="n" s="5">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="E15" t="n" s="5">
-        <v>2.04</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="s" s="4">
-        <v>58</v>
-      </c>
-      <c r="B16" t="s" s="4">
-        <v>59</v>
-      </c>
-      <c r="C16" t="n" s="7">
-        <v>10.7274</v>
-      </c>
-      <c r="D16" t="n" s="7">
-        <v>12.0</v>
-      </c>
-      <c r="E16" t="n" s="7">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="C17" t="n" s="5">
-        <v>7.2727</v>
-      </c>
-      <c r="D17" t="n" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="E17" t="n" s="5">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="1">
-        <v>62</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" t="n" s="1">
-        <v>675.45</v>
-      </c>
-      <c r="D18" t="n" s="1">
-        <v>102.0</v>
-      </c>
-      <c r="E18" t="n" s="1">
+      <c r="A16" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" t="n" s="1">
+        <v>334.27</v>
+      </c>
+      <c r="D16" t="n" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="E16" t="n" s="1">
         <v>100.0</v>
       </c>
     </row>
@@ -931,7 +734,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -942,13 +745,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -956,26 +759,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="1">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
       <c r="A5" t="s" s="1">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n" s="7">
         <v>7.0</v>
@@ -986,10 +789,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C7" t="n" s="5">
         <v>6.0</v>
@@ -1000,10 +803,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n" s="7">
         <v>5.0</v>
@@ -1014,10 +817,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n" s="5">
         <v>5.0</v>
@@ -1028,10 +831,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n" s="7">
         <v>3.0</v>
@@ -1042,10 +845,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n" s="5">
         <v>2.0</v>
@@ -1056,10 +859,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="C12" t="n" s="7">
         <v>2.0</v>
@@ -1070,10 +873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="C13" t="n" s="5">
         <v>2.0</v>
@@ -1084,10 +887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n" s="7">
         <v>1.0</v>
@@ -1098,10 +901,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n" s="5">
         <v>1.0</v>
@@ -1112,10 +915,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s" s="4">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C16" t="n" s="7">
         <v>1.0</v>
@@ -1126,10 +929,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n" s="5">
         <v>1.0</v>
@@ -1140,10 +943,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s" s="4">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C18" t="n" s="7">
         <v>1.0</v>
@@ -1154,10 +957,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C19" t="n" s="5">
         <v>1.0</v>
@@ -1168,10 +971,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="1">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s" s="4">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C20" t="n" s="1">
         <v>38.0</v>
@@ -1181,319 +984,13 @@
       </c>
     </row>
     <row r="21"/>
-    <row r="22">
-      <c r="A22" t="s" s="1">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="C23" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D23" t="n" s="5">
-        <v>12.7273</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="4">
-        <v>58</v>
-      </c>
-      <c r="B24" t="s" s="4">
-        <v>59</v>
-      </c>
-      <c r="C24" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="D24" t="n" s="7">
-        <v>0.9091</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="1">
-        <v>66</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="C25" t="n" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="D25" t="n" s="1">
-        <v>13.64</v>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="s" s="1">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="4">
-        <v>42</v>
-      </c>
-      <c r="B28" t="s" s="4">
-        <v>43</v>
-      </c>
-      <c r="C28" t="n" s="7">
-        <v>30.0</v>
-      </c>
-      <c r="D28" t="n" s="7">
-        <v>32.7273</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C29" t="n" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="D29" t="n" s="5">
-        <v>63.1819</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="B30" t="s" s="4">
-        <v>41</v>
-      </c>
-      <c r="C30" t="n" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="D30" t="n" s="7">
-        <v>18.1819</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="C31" t="n" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="D31" t="n" s="5">
-        <v>4.3637</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="4">
-        <v>32</v>
-      </c>
-      <c r="B32" t="s" s="4">
-        <v>33</v>
-      </c>
-      <c r="C32" t="n" s="7">
-        <v>4.0</v>
-      </c>
-      <c r="D32" t="n" s="7">
-        <v>50.9091</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="C33" t="n" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="D33" t="n" s="5">
-        <v>38.1818</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="4">
-        <v>34</v>
-      </c>
-      <c r="B34" t="s" s="4">
-        <v>35</v>
-      </c>
-      <c r="C34" t="n" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="D34" t="n" s="7">
-        <v>21.1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="C35" t="n" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="D35" t="n" s="5">
-        <v>14.5454</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="4">
-        <v>56</v>
-      </c>
-      <c r="B36" t="s" s="4">
-        <v>57</v>
-      </c>
-      <c r="C36" t="n" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="D36" t="n" s="7">
-        <v>6.5364</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C37" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D37" t="n" s="5">
-        <v>23.5455</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="4">
-        <v>44</v>
-      </c>
-      <c r="B38" t="s" s="4">
-        <v>45</v>
-      </c>
-      <c r="C38" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="D38" t="n" s="7">
-        <v>15.3636</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="C39" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D39" t="n" s="5">
-        <v>14.5455</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="4">
-        <v>48</v>
-      </c>
-      <c r="B40" t="s" s="4">
-        <v>49</v>
-      </c>
-      <c r="C40" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="D40" t="n" s="7">
-        <v>14.4545</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="C41" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D41" t="n" s="5">
-        <v>9.9091</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="1">
-        <v>66</v>
-      </c>
-      <c r="B42" t="s" s="4">
-        <v>67</v>
-      </c>
-      <c r="C42" t="n" s="1">
-        <v>62.0</v>
-      </c>
-      <c r="D42" t="n" s="1">
-        <v>327.55</v>
-      </c>
-    </row>
-    <row r="43"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="4">
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A42:B42"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="12.73046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="7.9140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.73046875" customWidth="true" bestFit="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>70</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>71</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n" s="9">
-        <v>3323.0</v>
-      </c>
-      <c r="B2" s="12" t="n">
-        <f>(A2-C2)/C2</f>
-        <v>0.0</v>
-      </c>
-      <c r="C2" t="n" s="9">
-        <v>3615.0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>